--- a/data/availability/projects/palm-hills-developments/palm-hills-new-cairo.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-new-cairo.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -909,7 +909,6 @@
       <c r="G2" t="n">
         <v>114</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -920,7 +919,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -966,7 +965,6 @@
       <c r="G3" t="n">
         <v>131</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -977,7 +975,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1023,7 +1021,6 @@
       <c r="G4" t="n">
         <v>115</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1034,7 +1031,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1080,7 +1077,6 @@
       <c r="G5" t="n">
         <v>131</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1137,7 +1133,6 @@
       <c r="G6" t="n">
         <v>131</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1148,7 +1143,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1194,7 +1189,6 @@
       <c r="G7" t="n">
         <v>70</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1205,7 +1199,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1251,7 +1245,6 @@
       <c r="G8" t="n">
         <v>114</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1262,7 +1255,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1308,7 +1301,6 @@
       <c r="G9" t="n">
         <v>115</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1319,7 +1311,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1365,7 +1357,6 @@
       <c r="G10" t="n">
         <v>115</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1376,7 +1367,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1422,7 +1413,6 @@
       <c r="G11" t="n">
         <v>132</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1433,7 +1423,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,7 +1469,6 @@
       <c r="G12" t="n">
         <v>131</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1490,7 +1479,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1536,7 +1525,6 @@
       <c r="G13" t="n">
         <v>131</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1547,7 +1535,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1593,7 +1581,6 @@
       <c r="G14" t="n">
         <v>114</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1604,7 +1591,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1650,7 +1637,6 @@
       <c r="G15" t="n">
         <v>114.5</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1661,7 +1647,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1707,7 +1693,6 @@
       <c r="G16" t="n">
         <v>131</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1718,7 +1703,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1764,7 +1749,6 @@
       <c r="G17" t="n">
         <v>115</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1775,7 +1759,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1821,7 +1805,6 @@
       <c r="G18" t="n">
         <v>115</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1832,7 +1815,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1878,7 +1861,6 @@
       <c r="G19" t="n">
         <v>115</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1889,7 +1871,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1935,7 +1917,6 @@
       <c r="G20" t="n">
         <v>114</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1946,7 +1927,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1992,7 +1973,6 @@
       <c r="G21" t="n">
         <v>131</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2003,7 +1983,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2049,7 +2029,6 @@
       <c r="G22" t="n">
         <v>131</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2060,7 +2039,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2106,7 +2085,6 @@
       <c r="G23" t="n">
         <v>152</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2117,7 +2095,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2163,7 +2141,6 @@
       <c r="G24" t="n">
         <v>114</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2174,7 +2151,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2220,7 +2197,6 @@
       <c r="G25" t="n">
         <v>131</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2231,7 +2207,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2277,7 +2253,6 @@
       <c r="G26" t="n">
         <v>131</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2288,7 +2263,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2334,7 +2309,6 @@
       <c r="G27" t="n">
         <v>131</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2345,7 +2319,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2391,7 +2365,6 @@
       <c r="G28" t="n">
         <v>131</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2402,7 +2375,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2448,7 +2421,6 @@
       <c r="G29" t="n">
         <v>131</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2459,7 +2431,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2505,7 +2477,6 @@
       <c r="G30" t="n">
         <v>131</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2516,7 +2487,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2562,7 +2533,6 @@
       <c r="G31" t="n">
         <v>131</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2573,7 +2543,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2619,7 +2589,6 @@
       <c r="G32" t="n">
         <v>132</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2630,7 +2599,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2676,7 +2645,6 @@
       <c r="G33" t="n">
         <v>172</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2687,7 +2655,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2733,7 +2701,6 @@
       <c r="G34" t="n">
         <v>114</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2744,7 +2711,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2790,7 +2757,6 @@
       <c r="G35" t="n">
         <v>131</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2801,7 +2767,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2847,7 +2813,6 @@
       <c r="G36" t="n">
         <v>132</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2858,7 +2823,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2904,7 +2869,6 @@
       <c r="G37" t="n">
         <v>132</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2915,7 +2879,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2961,7 +2925,6 @@
       <c r="G38" t="n">
         <v>132</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2972,7 +2935,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3018,7 +2981,6 @@
       <c r="G39" t="n">
         <v>131</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3029,7 +2991,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3075,7 +3037,6 @@
       <c r="G40" t="n">
         <v>152</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3086,7 +3047,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3132,7 +3093,6 @@
       <c r="G41" t="n">
         <v>114</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3143,7 +3103,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3189,7 +3149,6 @@
       <c r="G42" t="n">
         <v>131</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3200,7 +3159,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3246,7 +3205,6 @@
       <c r="G43" t="n">
         <v>115</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3257,7 +3215,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3303,7 +3261,6 @@
       <c r="G44" t="n">
         <v>131</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3314,7 +3271,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3360,7 +3317,6 @@
       <c r="G45" t="n">
         <v>131</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3371,7 +3327,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3417,7 +3373,6 @@
       <c r="G46" t="n">
         <v>131</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3428,7 +3383,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3474,7 +3429,6 @@
       <c r="G47" t="n">
         <v>131</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3485,7 +3439,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3531,7 +3485,6 @@
       <c r="G48" t="n">
         <v>131</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3542,7 +3495,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3588,7 +3541,6 @@
       <c r="G49" t="n">
         <v>131</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3599,7 +3551,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3645,7 +3597,6 @@
       <c r="G50" t="n">
         <v>200</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3656,7 +3607,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3702,7 +3653,6 @@
       <c r="G51" t="n">
         <v>132</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3713,7 +3663,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3759,7 +3709,6 @@
       <c r="G52" t="n">
         <v>172</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3770,7 +3719,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3816,7 +3765,6 @@
       <c r="G53" t="n">
         <v>114</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3827,7 +3775,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3873,7 +3821,6 @@
       <c r="G54" t="n">
         <v>132</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3884,7 +3831,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3930,7 +3877,6 @@
       <c r="G55" t="n">
         <v>131</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3941,7 +3887,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3987,7 +3933,6 @@
       <c r="G56" t="n">
         <v>132</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3998,7 +3943,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4044,7 +3989,6 @@
       <c r="G57" t="n">
         <v>132</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4055,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4101,7 +4045,6 @@
       <c r="G58" t="n">
         <v>132</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4112,7 +4055,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4158,7 +4101,6 @@
       <c r="G59" t="n">
         <v>131</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4169,7 +4111,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4215,7 +4157,6 @@
       <c r="G60" t="n">
         <v>131</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4226,7 +4167,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4272,7 +4213,6 @@
       <c r="G61" t="n">
         <v>200</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4283,7 +4223,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4329,7 +4269,6 @@
       <c r="G62" t="n">
         <v>131</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4340,7 +4279,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4386,7 +4325,6 @@
       <c r="G63" t="n">
         <v>152</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4397,7 +4335,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4443,7 +4381,6 @@
       <c r="G64" t="n">
         <v>131</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4454,7 +4391,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4500,7 +4437,6 @@
       <c r="G65" t="n">
         <v>131</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4511,7 +4447,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4557,7 +4493,6 @@
       <c r="G66" t="n">
         <v>131</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4568,7 +4503,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4614,7 +4549,6 @@
       <c r="G67" t="n">
         <v>131</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4625,7 +4559,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4671,7 +4605,6 @@
       <c r="G68" t="n">
         <v>131</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4682,7 +4615,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4728,7 +4661,6 @@
       <c r="G69" t="n">
         <v>131</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4739,7 +4671,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4785,7 +4717,6 @@
       <c r="G70" t="n">
         <v>131</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4796,7 +4727,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4842,7 +4773,6 @@
       <c r="G71" t="n">
         <v>200</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4853,7 +4783,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4899,7 +4829,6 @@
       <c r="G72" t="n">
         <v>132</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4910,7 +4839,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4956,7 +4885,6 @@
       <c r="G73" t="n">
         <v>172</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4967,7 +4895,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5013,7 +4941,6 @@
       <c r="G74" t="n">
         <v>114</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5024,7 +4951,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5070,7 +4997,6 @@
       <c r="G75" t="n">
         <v>132</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5081,7 +5007,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5127,7 +5053,6 @@
       <c r="G76" t="n">
         <v>131</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5138,7 +5063,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5184,7 +5109,6 @@
       <c r="G77" t="n">
         <v>132</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5195,7 +5119,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5241,7 +5165,6 @@
       <c r="G78" t="n">
         <v>132</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5252,7 +5175,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5298,7 +5221,6 @@
       <c r="G79" t="n">
         <v>131</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5309,7 +5231,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5355,7 +5277,6 @@
       <c r="G80" t="n">
         <v>131</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5366,7 +5287,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5412,7 +5333,6 @@
       <c r="G81" t="n">
         <v>200</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5423,7 +5343,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5469,7 +5389,6 @@
       <c r="G82" t="n">
         <v>131</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5480,7 +5399,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5526,7 +5445,6 @@
       <c r="G83" t="n">
         <v>131</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5537,7 +5455,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5583,7 +5501,6 @@
       <c r="G84" t="n">
         <v>131</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5594,7 +5511,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5640,7 +5557,6 @@
       <c r="G85" t="n">
         <v>131</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5651,7 +5567,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5697,7 +5613,6 @@
       <c r="G86" t="n">
         <v>131</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5708,7 +5623,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5754,7 +5669,6 @@
       <c r="G87" t="n">
         <v>114</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5765,7 +5679,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5811,7 +5725,6 @@
       <c r="G88" t="n">
         <v>132</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5822,7 +5735,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5868,7 +5781,6 @@
       <c r="G89" t="n">
         <v>131</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5879,7 +5791,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5925,7 +5837,6 @@
       <c r="G90" t="n">
         <v>132</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5936,7 +5847,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5982,7 +5893,6 @@
       <c r="G91" t="n">
         <v>132</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5993,7 +5903,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6039,7 +5949,6 @@
       <c r="G92" t="n">
         <v>131</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6050,7 +5959,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6096,7 +6005,6 @@
       <c r="G93" t="n">
         <v>131</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6107,7 +6015,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6153,7 +6061,6 @@
       <c r="G94" t="n">
         <v>70</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6164,7 +6071,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6210,7 +6117,6 @@
       <c r="G95" t="n">
         <v>114</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6221,7 +6127,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6267,7 +6173,6 @@
       <c r="G96" t="n">
         <v>70</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6278,7 +6183,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6324,7 +6229,6 @@
       <c r="G97" t="n">
         <v>131</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6335,7 +6239,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6381,7 +6285,6 @@
       <c r="G98" t="n">
         <v>115</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6392,7 +6295,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6438,7 +6341,6 @@
       <c r="G99" t="n">
         <v>70</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6449,7 +6351,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6495,7 +6397,6 @@
       <c r="G100" t="n">
         <v>131</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6506,7 +6407,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6552,7 +6453,6 @@
       <c r="G101" t="n">
         <v>115</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6563,7 +6463,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6609,7 +6509,6 @@
       <c r="G102" t="n">
         <v>70</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6620,7 +6519,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6666,7 +6565,6 @@
       <c r="G103" t="n">
         <v>131</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6677,7 +6575,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6723,7 +6621,6 @@
       <c r="G104" t="n">
         <v>70</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6734,7 +6631,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6780,7 +6677,6 @@
       <c r="G105" t="n">
         <v>131</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6791,7 +6687,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6837,7 +6733,6 @@
       <c r="G106" t="n">
         <v>70</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6848,7 +6743,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6894,7 +6789,6 @@
       <c r="G107" t="n">
         <v>131</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6905,7 +6799,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6951,7 +6845,6 @@
       <c r="G108" t="n">
         <v>114.5</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6962,7 +6855,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7008,7 +6901,6 @@
       <c r="G109" t="n">
         <v>70</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7019,7 +6911,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7065,7 +6957,6 @@
       <c r="G110" t="n">
         <v>131</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7076,7 +6967,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7122,7 +7013,6 @@
       <c r="G111" t="n">
         <v>200</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7133,7 +7023,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
